--- a/ksoft_old/docs/records/Receipt_Cod_Observa_Enum.xlsx
+++ b/ksoft_old/docs/records/Receipt_Cod_Observa_Enum.xlsx
@@ -1282,13 +1282,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DCA71E21-780B-48C0-953B-FE0D1D2E2059}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D59EA398-8589-4293-AB92-847217503560}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6BBE3CB6-FE00-4A70-B855-87921BDEA013}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{950EEF21-8AFE-4E56-AFBB-44D7CBE0A246}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C1B6F0CE-BE6C-4A93-A38E-07DEE4E17DF5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4266D6E6-D3EC-41D5-B2E8-92F58F276FB6}"/>
 </file>
--- a/ksoft_old/docs/records/Receipt_Cod_Observa_Enum.xlsx
+++ b/ksoft_old/docs/records/Receipt_Cod_Observa_Enum.xlsx
@@ -1282,13 +1282,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D59EA398-8589-4293-AB92-847217503560}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6B561AAE-9F82-4630-B91E-1573D2C09A3A}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{950EEF21-8AFE-4E56-AFBB-44D7CBE0A246}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4B218E62-8FF3-42EF-8C79-F2B3E29C31A6}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4266D6E6-D3EC-41D5-B2E8-92F58F276FB6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AF590F61-ADA2-42B1-B30D-A97523AC6BF5}"/>
 </file>
--- a/ksoft_old/docs/records/Receipt_Cod_Observa_Enum.xlsx
+++ b/ksoft_old/docs/records/Receipt_Cod_Observa_Enum.xlsx
@@ -1282,13 +1282,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6B561AAE-9F82-4630-B91E-1573D2C09A3A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DCA71E21-780B-48C0-953B-FE0D1D2E2059}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4B218E62-8FF3-42EF-8C79-F2B3E29C31A6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6BBE3CB6-FE00-4A70-B855-87921BDEA013}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AF590F61-ADA2-42B1-B30D-A97523AC6BF5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C1B6F0CE-BE6C-4A93-A38E-07DEE4E17DF5}"/>
 </file>